--- a/data/trans_camb/KIDM_C_3_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,41</t>
+          <t>0,04; 17,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 16,95</t>
+          <t>-1,31; 15,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 0,0</t>
+          <t>-10,14; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 21,84</t>
+          <t>-0,09; 19,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 31,84</t>
+          <t>5,59; 30,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 2,99</t>
+          <t>-11,47; 1,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 16,09</t>
+          <t>2,34; 15,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,93</t>
+          <t>5,03; 20,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,98</t>
+          <t>-5,79; 1,02</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,08; —</t>
+          <t>-59,71; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,06; —</t>
+          <t>19,19; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1732,58</t>
+          <t>11,49; inf</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,99; 2070,96</t>
+          <t>66,63; 2076,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 29,66</t>
+          <t>4,11; 29,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 23,02</t>
+          <t>1,43; 22,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 5,92</t>
+          <t>-9,62; 5,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 22,37</t>
+          <t>4,35; 24,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 8,03</t>
+          <t>-5,24; 7,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,83</t>
+          <t>-4,42; 8,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 22,79</t>
+          <t>6,78; 22,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 13,32</t>
+          <t>0,79; 13,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,79</t>
+          <t>-4,88; 5,63</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,86; —</t>
+          <t>21,3; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,77; —</t>
+          <t>-16,14; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 22,92</t>
+          <t>0,48; 23,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 4,48</t>
+          <t>-12,08; 4,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 16,39</t>
+          <t>-7,14; 16,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 19,08</t>
+          <t>-2,36; 19,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 18,96</t>
+          <t>-0,31; 18,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -1,31</t>
+          <t>-10,71; -1,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 17,23</t>
+          <t>2,46; 17,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 10,93</t>
+          <t>-2,27; 11,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 2,67</t>
+          <t>-6,98; 2,61</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,72; —</t>
+          <t>-31,59; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,18; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 1265,9</t>
+          <t>-36,91; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,27; 914,06</t>
+          <t>15,77; 863,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 526,82</t>
+          <t>-51,33; 623,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,68; 24,1</t>
+          <t>7,05; 23,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,13</t>
+          <t>-5,64; 6,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 7,25</t>
+          <t>-8,73; 6,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,1</t>
+          <t>1,52; 13,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 9,75</t>
+          <t>-1,64; 9,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,54</t>
+          <t>-4,72; 4,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 15,82</t>
+          <t>5,19; 16,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,22</t>
+          <t>-2,37; 5,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 2,89</t>
+          <t>-5,12; 3,38</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,09; 578,52</t>
+          <t>61,82; 603,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,38; 167,22</t>
+          <t>-57,57; 176,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,8; 142,14</t>
+          <t>-92,51; 134,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1321,93</t>
+          <t>-13,16; 1056,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 932,21</t>
+          <t>-46,78; 826,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,99; 488,76</t>
+          <t>65,89; 497,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 194,66</t>
+          <t>-34,82; 182,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 92,12</t>
+          <t>-76,96; 108,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 14,43</t>
+          <t>-2,28; 14,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 10,47</t>
+          <t>-5,05; 11,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 13,32</t>
+          <t>-6,44; 14,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 11,9</t>
+          <t>-3,39; 12,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 16,9</t>
+          <t>-1,03; 16,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 1,88</t>
+          <t>-10,94; 1,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,5</t>
+          <t>-0,8; 10,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 11,11</t>
+          <t>-0,78; 11,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 2,52</t>
+          <t>-7,32; 3,7</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 627,12</t>
+          <t>-28,62; 620,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 562,33</t>
+          <t>-52,51; 514,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 1021,22</t>
+          <t>-74,38; 619,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 366,83</t>
+          <t>-34,6; 394,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 537,26</t>
+          <t>-14,34; 494,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 118,42</t>
+          <t>-100,0; 115,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 234,38</t>
+          <t>-12,16; 245,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 249,38</t>
+          <t>-11,41; 245,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-81,16; 75,8</t>
+          <t>-77,69; 95,64</t>
         </is>
       </c>
     </row>
@@ -1757,27 +1757,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 16,98</t>
+          <t>-3,47; 16,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 16,87</t>
+          <t>-3,11; 16,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 0,0</t>
+          <t>-9,96; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,59; 15,8</t>
+          <t>1,62; 14,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 13,12</t>
+          <t>1,76; 14,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 11,11</t>
+          <t>-0,21; 11,05</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 11,38</t>
+          <t>0,33; 11,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,0</t>
+          <t>-5,7; 0,0</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-40,87; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,97; 14,82</t>
+          <t>6,62; 14,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,01</t>
+          <t>0,45; 7,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 2,33</t>
+          <t>-4,16; 2,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,74</t>
+          <t>3,88; 10,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,95</t>
+          <t>2,89; 9,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,34</t>
+          <t>-4,37; 0,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,72</t>
+          <t>6,19; 11,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,58</t>
+          <t>2,91; 7,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,29</t>
+          <t>-3,31; 0,29</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>100,18; 438,96</t>
+          <t>95,18; 392,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8,17; 208,07</t>
+          <t>2,67; 204,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 61,84</t>
+          <t>-66,36; 61,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>77,87; 414,69</t>
+          <t>64,54; 400,27</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>60,21; 392,17</t>
+          <t>49,56; 371,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 28,23</t>
+          <t>-85,76; 26,01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>119,71; 358,19</t>
+          <t>117,92; 338,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>46,76; 221,23</t>
+          <t>53,12; 233,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-68,41; 7,24</t>
+          <t>-65,22; 10,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_C_3_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 17,45</t>
+          <t>0,12; 17,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 15,76</t>
+          <t>-0,44; 16,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,0</t>
+          <t>-8,92; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 19,9</t>
+          <t>0,67; 21,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 30,46</t>
+          <t>5,2; 30,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 1,67</t>
+          <t>-10,63; 2,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 15,96</t>
+          <t>2,4; 16,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 20,98</t>
+          <t>4,74; 20,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,02</t>
+          <t>-6,36; 0,96</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; —</t>
+          <t>-49,36; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,19; —</t>
+          <t>24,12; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,49; inf</t>
+          <t>7,95; 1572,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,63; 2076,0</t>
+          <t>41,32; 1896,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 29,36</t>
+          <t>3,62; 28,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 22,17</t>
+          <t>1,76; 22,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 5,76</t>
+          <t>-9,77; 5,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 24,07</t>
+          <t>2,84; 23,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,82</t>
+          <t>-4,23; 7,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 8,98</t>
+          <t>-4,48; 8,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 22,81</t>
+          <t>5,59; 21,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 13,49</t>
+          <t>0,39; 12,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,63</t>
+          <t>-4,83; 5,78</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,3; —</t>
+          <t>44,06; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,14; —</t>
+          <t>-15,91; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 23,01</t>
+          <t>-0,24; 21,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 4,32</t>
+          <t>-11,77; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 16,32</t>
+          <t>-7,62; 17,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 19,0</t>
+          <t>-1,37; 19,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 18,61</t>
+          <t>-0,73; 18,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -1,31</t>
+          <t>-10,65; -1,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 17,67</t>
+          <t>2,73; 17,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 11,25</t>
+          <t>-1,91; 11,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 2,61</t>
+          <t>-6,75; 2,97</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; —</t>
+          <t>-42,51; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,18; —</t>
+          <t>-45,25; 1657,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,91; —</t>
+          <t>-42,55; 1216,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,77; 863,37</t>
+          <t>24,4; 843,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 623,26</t>
+          <t>-43,16; 582,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 23,35</t>
+          <t>7,13; 24,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 6,15</t>
+          <t>-5,64; 6,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 6,59</t>
+          <t>-9,21; 6,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,32</t>
+          <t>2,09; 13,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 9,31</t>
+          <t>-1,42; 9,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,86</t>
+          <t>-4,91; 4,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,07</t>
+          <t>5,94; 16,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,96</t>
+          <t>-1,91; 6,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 3,38</t>
+          <t>-5,18; 3,19</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>61,82; 603,31</t>
+          <t>53,67; 633,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 176,75</t>
+          <t>-57,88; 174,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 134,26</t>
+          <t>-93,38; 137,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 1056,64</t>
+          <t>10,96; 1213,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 826,31</t>
+          <t>-58,56; 800,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,89; 497,14</t>
+          <t>77,02; 587,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 182,17</t>
+          <t>-28,65; 205,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,96; 108,04</t>
+          <t>-79,3; 107,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 14,42</t>
+          <t>-2,37; 14,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 11,12</t>
+          <t>-4,86; 10,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 14,19</t>
+          <t>-6,73; 11,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 12,19</t>
+          <t>-3,15; 12,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 16,16</t>
+          <t>-0,42; 16,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 1,97</t>
+          <t>-10,78; 2,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 10,48</t>
+          <t>-0,19; 10,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 11,32</t>
+          <t>-1,02; 10,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,7</t>
+          <t>-7,32; 3,52</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 620,6</t>
+          <t>-30,45; 504,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 514,34</t>
+          <t>-51,23; 429,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,38; 619,63</t>
+          <t>-79,01; 497,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 394,49</t>
+          <t>-33,7; 409,35</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 494,38</t>
+          <t>-9,01; 564,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,34</t>
+          <t>-100,0; 156,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 245,99</t>
+          <t>-3,35; 258,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 245,17</t>
+          <t>-11,6; 275,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,69; 95,64</t>
+          <t>-80,59; 95,46</t>
         </is>
       </c>
     </row>
@@ -1757,27 +1757,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 16,66</t>
+          <t>-3,15; 15,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 16,4</t>
+          <t>-3,02; 16,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 0,0</t>
+          <t>-10,03; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,08</t>
+          <t>1,58; 14,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,54</t>
+          <t>1,78; 14,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 11,05</t>
+          <t>0,09; 12,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 11,76</t>
+          <t>0,12; 11,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,0</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,87; —</t>
+          <t>-57,62; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,61</t>
+          <t>6,62; 14,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 7,12</t>
+          <t>0,5; 7,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,23</t>
+          <t>-4,27; 2,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,63</t>
+          <t>3,89; 10,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,56</t>
+          <t>3,45; 10,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,25</t>
+          <t>-4,24; 0,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,6</t>
+          <t>6,28; 11,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,76</t>
+          <t>2,94; 7,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,29</t>
+          <t>-3,56; 0,22</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>95,18; 392,19</t>
+          <t>100,64; 451,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2,67; 204,08</t>
+          <t>6,06; 208,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 61,36</t>
+          <t>-67,17; 62,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>64,54; 400,27</t>
+          <t>74,83; 407,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>49,56; 371,85</t>
+          <t>58,0; 385,16</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 26,01</t>
+          <t>-85,64; 22,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>117,92; 338,2</t>
+          <t>115,57; 351,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>53,12; 233,3</t>
+          <t>53,04; 218,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-65,22; 10,48</t>
+          <t>-66,32; 11,96</t>
         </is>
       </c>
     </row>
